--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.79739166612996</v>
+        <v>2.404576145746118</v>
       </c>
       <c r="D2" t="n">
-        <v>15.98497002186063</v>
+        <v>2.597557628552352</v>
       </c>
       <c r="E2" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F2" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.02203855465172</v>
+        <v>8.291081265130906</v>
       </c>
       <c r="D3" t="n">
-        <v>2.386303510546054</v>
+        <v>0.3877743204637338</v>
       </c>
       <c r="E3" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F3" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.06574124980415</v>
+        <v>10.41068295309317</v>
       </c>
       <c r="D4" t="n">
-        <v>19.61062564744063</v>
+        <v>3.186726667709102</v>
       </c>
       <c r="E4" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F4" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.34755769858716</v>
+        <v>8.181478126020414</v>
       </c>
       <c r="D5" t="n">
-        <v>7.695185544576847</v>
+        <v>1.250467650993738</v>
       </c>
       <c r="E5" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F5" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.29535539074835</v>
+        <v>5.897995250996606</v>
       </c>
       <c r="D6" t="n">
-        <v>6.729050194466313</v>
+        <v>1.093470656600776</v>
       </c>
       <c r="E6" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F6" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.67222475968951</v>
+        <v>10.50923652344955</v>
       </c>
       <c r="D7" t="n">
-        <v>31.97406565243814</v>
+        <v>5.195785668521198</v>
       </c>
       <c r="E7" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F7" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.91934630298678</v>
+        <v>3.236893774235352</v>
       </c>
       <c r="D8" t="n">
-        <v>19.50896693723298</v>
+        <v>3.17020712730036</v>
       </c>
       <c r="E8" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F8" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.07067228413936</v>
+        <v>5.536484246172646</v>
       </c>
       <c r="D9" t="n">
-        <v>18.05580352261931</v>
+        <v>2.934068072425638</v>
       </c>
       <c r="E9" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F9" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.8832629235256</v>
+        <v>5.66853022507291</v>
       </c>
       <c r="D10" t="n">
-        <v>9.613293967255492</v>
+        <v>1.562160269679018</v>
       </c>
       <c r="E10" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F10" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.8016822899437</v>
+        <v>4.680273372115852</v>
       </c>
       <c r="D11" t="n">
-        <v>29.26324650930552</v>
+        <v>4.755277557762147</v>
       </c>
       <c r="E11" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F11" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.97540616789465</v>
+        <v>5.846003502282881</v>
       </c>
       <c r="D12" t="n">
-        <v>34.80973283883711</v>
+        <v>5.656581586311031</v>
       </c>
       <c r="E12" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F12" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.19686723338133</v>
+        <v>4.906990925424465</v>
       </c>
       <c r="D13" t="n">
-        <v>27.28341498426595</v>
+        <v>4.433554934943216</v>
       </c>
       <c r="E13" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F13" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.2929693086062</v>
+        <v>7.035107512648507</v>
       </c>
       <c r="D14" t="n">
-        <v>42.00099785788509</v>
+        <v>6.825162151906327</v>
       </c>
       <c r="E14" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F14" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.09009978670092</v>
+        <v>7.977141215338899</v>
       </c>
       <c r="D15" t="n">
-        <v>47.90631548608857</v>
+        <v>7.784776266489392</v>
       </c>
       <c r="E15" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F15" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>53.66106741974269</v>
+        <v>8.719923455708187</v>
       </c>
       <c r="D16" t="n">
-        <v>51.86516998656668</v>
+        <v>8.428090122817085</v>
       </c>
       <c r="E16" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F16" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.06154670097737</v>
+        <v>4.235001338908823</v>
       </c>
       <c r="D17" t="n">
-        <v>8.020920146088097</v>
+        <v>1.303399523739316</v>
       </c>
       <c r="E17" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F17" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>25.86255257828822</v>
+        <v>4.202664793971836</v>
       </c>
       <c r="D18" t="n">
-        <v>25.14932398012891</v>
+        <v>4.086765146770948</v>
       </c>
       <c r="E18" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F18" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1.652128718575569</v>
+        <v>0.26847091676853</v>
       </c>
       <c r="D19" t="n">
-        <v>3.835810966622209</v>
+        <v>0.623319282076109</v>
       </c>
       <c r="E19" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F19" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>34.16137696586752</v>
+        <v>5.551223756953472</v>
       </c>
       <c r="D20" t="n">
-        <v>6.686333840050343</v>
+        <v>1.086529249008181</v>
       </c>
       <c r="E20" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F20" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>44.6425966247205</v>
+        <v>7.254421951517081</v>
       </c>
       <c r="D21" t="n">
-        <v>8.354666202523848</v>
+        <v>1.357633257910125</v>
       </c>
       <c r="E21" t="n">
-        <v>15.50529050274112</v>
+        <v>2.519609706695431</v>
       </c>
       <c r="F21" t="n">
-        <v>14.62166897932621</v>
+        <v>2.376021209140509</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
